--- a/data/masterdata/Processes.xlsx
+++ b/data/masterdata/Processes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beotalk-my.sharepoint.com/personal/tora_bang-olufsen_dk/Documents/Dokumenter/GitHub/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tora\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{93F8EE0A-A50F-431E-9917-0363C979C03B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F34AE1F4-4619-4E22-A698-7417D45890DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{ED266DC8-543B-4E4B-92C9-0B165DC4D186}"/>
+    <workbookView xWindow="-49185" yWindow="6210" windowWidth="20340" windowHeight="6720" xr2:uid="{ED266DC8-543B-4E4B-92C9-0B165DC4D186}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
   <si>
     <t>Process ID</t>
   </si>
@@ -48,6 +48,57 @@
   </si>
   <si>
     <t>Technology ID</t>
+  </si>
+  <si>
+    <t>CNC Machining</t>
+  </si>
+  <si>
+    <t>Die Casting</t>
+  </si>
+  <si>
+    <t>HP Multi Jet Fusion</t>
+  </si>
+  <si>
+    <t>CNC_STD</t>
+  </si>
+  <si>
+    <t>CNC</t>
+  </si>
+  <si>
+    <t>DC_STD</t>
+  </si>
+  <si>
+    <t>DC</t>
+  </si>
+  <si>
+    <t>HPDC_STD</t>
+  </si>
+  <si>
+    <t>HPDC</t>
+  </si>
+  <si>
+    <t>IM_STD</t>
+  </si>
+  <si>
+    <t>Injection Molding</t>
+  </si>
+  <si>
+    <t>IM</t>
+  </si>
+  <si>
+    <t>SC_STD</t>
+  </si>
+  <si>
+    <t>Sand Casting</t>
+  </si>
+  <si>
+    <t>SC</t>
+  </si>
+  <si>
+    <t>MJF_STD</t>
+  </si>
+  <si>
+    <t>MJF</t>
   </si>
 </sst>
 </file>
@@ -89,10 +140,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -428,14 +485,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{018ECA31-FAFA-4A6C-B87A-CFAD389D9BAF}">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="3" width="27.26953125" customWidth="1"/>
+    <col min="1" max="3" width="20.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -443,6 +500,72 @@
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
